--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.34742747597319</v>
+        <v>3.306456964845644</v>
       </c>
       <c r="D2" t="n">
-        <v>20.48089112762697</v>
+        <v>3.328144808239383</v>
       </c>
       <c r="E2" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F2" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.6145506327825</v>
+        <v>4.487364477827156</v>
       </c>
       <c r="D3" t="n">
-        <v>27.65262243713392</v>
+        <v>4.493551146034263</v>
       </c>
       <c r="E3" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F3" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.90023159117924</v>
+        <v>4.858787633566626</v>
       </c>
       <c r="D4" t="n">
-        <v>30.10035405027297</v>
+        <v>4.891307533169357</v>
       </c>
       <c r="E4" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F4" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.77110651855217</v>
+        <v>6.137804809264728</v>
       </c>
       <c r="D5" t="n">
-        <v>39.16991525212728</v>
+        <v>6.365111228470682</v>
       </c>
       <c r="E5" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F5" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.87550664564854</v>
+        <v>10.37976982991789</v>
       </c>
       <c r="D6" t="n">
-        <v>55.93882816035386</v>
+        <v>9.090059576057504</v>
       </c>
       <c r="E6" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F6" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>66.08214158002417</v>
+        <v>10.73834800675393</v>
       </c>
       <c r="D7" t="n">
-        <v>64.93845431710034</v>
+        <v>10.5524988265288</v>
       </c>
       <c r="E7" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F7" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.49083190422807</v>
+        <v>9.667260184437062</v>
       </c>
       <c r="D8" t="n">
-        <v>59.82515048924278</v>
+        <v>9.721586954501952</v>
       </c>
       <c r="E8" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F8" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>78.74328314403695</v>
+        <v>12.79578351090601</v>
       </c>
       <c r="D9" t="n">
-        <v>28.57008925432331</v>
+        <v>4.642639503827538</v>
       </c>
       <c r="E9" t="n">
-        <v>20.21337304379649</v>
+        <v>3.28467311961693</v>
       </c>
       <c r="F9" t="n">
-        <v>15.91471780182167</v>
+        <v>2.586141642796022</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
